--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -553,11 +553,11 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OK - 9/19 articles in past week (from https://feeds.bbci.co.uk/news/world/latin_america/rss.xml)</t>
+          <t>OK - 8/19 articles in past week (from https://feeds.bbci.co.uk/news/world/latin_america/rss.xml)</t>
         </is>
       </c>
     </row>
@@ -603,11 +603,11 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OK - 4/4 articles in past week (from https://www.reforma.com/rss/portada.xml)</t>
+          <t>OK - 6/6 articles in past week (from https://www.reforma.com/rss/portada.xml)</t>
         </is>
       </c>
     </row>
@@ -628,36 +628,36 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OK - 47/47 articles in past week (from https://expansion.mx/rss)</t>
+          <t>OK - 50/50 articles in past week (from https://expansion.mx/rss)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>El Universal</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>free</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>OK - 100/100 articles in past week (from https://eluniversal.com.mx/arc/outboundfeeds/rss/?outputType=xml)</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>HTTP 404: https://www.eluniversal.com.mx/rss.xml</t>
         </is>
       </c>
     </row>

--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -764,12 +764,12 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Fintech Expert</t>
+          <t>El CEO</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -778,143 +778,143 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OK - 0/1 articles in past week (from https://fintechexpert.substack.com/feed)</t>
+          <t>OK - 10/10 articles in past week (from https://elceo.com/feed/)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Alto Nivel</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>OK - 30/30 articles in past week (from https://www.altonivel.com.mx/feed/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>iupana</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>OK - 8/10 articles in past week (from https://iupana.com/feed/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>América Economía</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>OK - 0/10 articles in past week (from https://americaeconomia.com/rss.xml)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Fintech Expert</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>paid</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>OK - 0/1 articles in past week (from https://fintechexpert.substack.com/feed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Fintech Hub</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>paid</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>OK - 0/10 articles in past week (from https://fintechhub.com.mx/feed/)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Ground News</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Paid subscription required, no public RSS/API available.  |  Suggestion: Consider using their mobile app manually, or check if subscription includes API access.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>El Lago de los Business (LinkedIn)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: Follow manually, or use Google Alerts for 'El Lago de los Business' as a proxy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>El CEO (LinkedIn)</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: Follow manually, or use Google Alerts for 'El CEO Mexico' as a proxy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Jeanette Leyva Reus (LinkedIn)</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: She writes for El Financiero -- already captured via that RSS feed. Filter by her byline.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>El Lago de los Business (YouTube)</t>
+          <t>Ground News</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -931,6 +931,106 @@
         <v>0</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Paid subscription required, no public RSS/API available.  |  Suggestion: Consider using their mobile app manually, or check if subscription includes API access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>El Lago de los Business (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: Follow manually, or use Google Alerts for 'El Lago de los Business' as a proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>El CEO (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: Follow manually, or use Google Alerts for 'El CEO Mexico' as a proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Jeanette Leyva Reus (LinkedIn)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>LinkedIn actively blocks automated scraping; no RSS feed.  |  Suggestion: She writes for El Financiero -- already captured via that RSS feed. Filter by her byline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>El Lago de los Business (YouTube)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Channel ID is unknown (placeholder 'XXX' in config); video content requires transcription.  |  Suggestion: Find the real channel ID from YouTube, then use: https://www.youtube.com/feeds/videos.xml?channel_id=REAL_ID</t>
         </is>

--- a/source_status.xlsx
+++ b/source_status.xlsx
@@ -553,11 +553,11 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OK - 8/19 articles in past week (from https://feeds.bbci.co.uk/news/world/latin_america/rss.xml)</t>
+          <t>OK - 14/18 articles in past week (from https://feeds.bbci.co.uk/news/world/latin_america/rss.xml)</t>
         </is>
       </c>
     </row>
@@ -587,27 +587,27 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Reforma</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>OK - 6/6 articles in past week (from https://www.reforma.com/rss/portada.xml)</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Feed parsed but 0 entries (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -628,36 +628,36 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OK - 50/50 articles in past week (from https://expansion.mx/rss)</t>
+          <t>OK - 48/48 articles in past week (from https://expansion.mx/rss)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>El Universal</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>HTTP 404: https://www.eluniversal.com.mx/rss.xml</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>OK - 100/100 articles in past week (from https://eluniversal.com.mx/arc/outboundfeeds/rss/?outputType=xml)</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>HTTP 404: https://eleconomista.com.mx/arc/outboundfeeds/rss/</t>
+          <t>Connection error: https://eleconomista.com.mx/arc/outboundfeeds/rss/</t>
         </is>
       </c>
     </row>
@@ -728,36 +728,36 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>OK - 99/100 articles in past week (from https://bloomberglinea.com/arc/outboundfeeds/rss/?outputType=xml)</t>
+          <t>OK - 98/100 articles in past week (from https://bloomberglinea.com/arc/outboundfeeds/rss/?outputType=xml)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Mexico News Daily</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>OK - 10/10 articles in past week (from https://mexiconewsdaily.com/feed/)</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Connection error: https://mexiconewsdaily.com/feed/</t>
         </is>
       </c>
     </row>
@@ -812,52 +812,52 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>iupana</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>OK - 8/10 articles in past week (from https://iupana.com/feed/)</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Connection error: https://iupana.com/feed/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>América Economía</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>OK - 0/10 articles in past week (from https://americaeconomia.com/rss.xml)</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>HTTP 404: https://americaeconomia.com/feed/</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OK - 0/10 articles in past week (from https://fintechhub.com.mx/feed/)</t>
+          <t>OK - 0/10 articles in past week (from http://fintechhub.com.mx/feed/)</t>
         </is>
       </c>
     </row>
